--- a/tools/luban/MiniTemplate/Datas/#demo.reward.xlsx
+++ b/tools/luban/MiniTemplate/Datas/#demo.reward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="24045" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -80,6 +80,9 @@
     <t>m2</t>
   </si>
   <si>
+    <t>m3</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -104,7 +107,7 @@
     <t>array,string</t>
   </si>
   <si>
-    <t>(list#sep=,),int</t>
+    <t>(list#sep=,#size=3),int</t>
   </si>
   <si>
     <t>array,test.Item</t>
@@ -116,6 +119,9 @@
     <t>(map#sep=,|),int,int</t>
   </si>
   <si>
+    <t>(set#sep=,),int</t>
+  </si>
+  <si>
     <t>READ</t>
   </si>
   <si>
@@ -185,7 +191,7 @@
     <t>cd</t>
   </si>
   <si>
-    <t>11,22</t>
+    <t>11,22,33</t>
   </si>
   <si>
     <t>abc</t>
@@ -197,6 +203,9 @@
     <t>1,2|3,4</t>
   </si>
   <si>
+    <t>1,2</t>
+  </si>
+  <si>
     <t>1002,1</t>
   </si>
   <si>
@@ -218,7 +227,7 @@
     <t>三四</t>
   </si>
   <si>
-    <t>33,44</t>
+    <t>33,44,22</t>
   </si>
   <si>
     <t>奖励3</t>
@@ -233,7 +242,7 @@
     <t>1001,3</t>
   </si>
   <si>
-    <t>55,66</t>
+    <t>55,66,77</t>
   </si>
   <si>
     <t>奖励4</t>
@@ -248,7 +257,7 @@
     <t>7啊</t>
   </si>
   <si>
-    <t>77,88</t>
+    <t>77,88,88</t>
   </si>
 </sst>
 </file>
@@ -261,14 +270,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -726,160 +728,157 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1206,19 +1205,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="6" max="6" width="19.625" customWidth="1"/>
-    <col min="19" max="19" width="13.75" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
+    <col min="19" max="19" width="30.5" customWidth="1"/>
+    <col min="20" max="20" width="22.625" customWidth="1"/>
     <col min="21" max="21" width="5.5" customWidth="1"/>
     <col min="22" max="22" width="7.125" customWidth="1"/>
     <col min="23" max="23" width="4.5" customWidth="1"/>
     <col min="24" max="24" width="6.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1278,83 +1277,89 @@
       <c r="Y1" t="s">
         <v>16</v>
       </c>
+      <c r="Z1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N3" t="s">
         <v>5</v>
@@ -1364,82 +1369,78 @@
       </c>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
-      <c r="S3"/>
-      <c r="T3"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
-      <c r="S4"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
-      <c r="S5"/>
       <c r="T5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:26">
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -1451,10 +1452,10 @@
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -1469,53 +1470,56 @@
         <v>3</v>
       </c>
       <c r="P6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R6" t="s">
+        <v>53</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="T6" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="T6" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="U6">
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>53</v>
-      </c>
-      <c r="W6" s="3">
+        <v>55</v>
+      </c>
+      <c r="W6" s="2">
         <v>2</v>
       </c>
-      <c r="X6" s="3" t="s">
-        <v>54</v>
+      <c r="X6" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="Y6" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
-      <c r="S7" s="3"/>
-      <c r="T7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
+    <row r="7" spans="1:26">
+      <c r="S7" s="2"/>
+      <c r="T7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:26">
       <c r="B8">
         <v>1002</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -1527,10 +1531,10 @@
         <v>22</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1542,32 +1546,29 @@
         <v>2</v>
       </c>
       <c r="P8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Q8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="R8" t="s">
-        <v>62</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="T8"/>
-      <c r="U8"/>
-      <c r="V8"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:26">
       <c r="B9">
         <v>1003</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E9">
         <v>1000</v>
@@ -1582,7 +1583,7 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -1594,7 +1595,7 @@
         <v>3</v>
       </c>
       <c r="P9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -1603,18 +1604,18 @@
         <v>6</v>
       </c>
       <c r="S9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:26">
       <c r="B10">
         <v>1004</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E10">
         <v>10000</v>
@@ -1629,7 +1630,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1637,7 +1638,6 @@
       <c r="K10">
         <v>1</v>
       </c>
-      <c r="L10"/>
       <c r="M10">
         <v>1</v>
       </c>
@@ -1648,16 +1648,16 @@
         <v>2</v>
       </c>
       <c r="P10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="R10">
         <v>98</v>
       </c>
       <c r="S10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
